--- a/artfynd/S 930-2023 artfynd.xlsx
+++ b/artfynd/S 930-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY67"/>
+  <dimension ref="A1:AZ67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130883908</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130840941</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130835933</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1064,6 +1084,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130840940</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1185,6 +1210,11 @@
           <t>Fågelinventering i Uvberget 2024</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122369823</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1292,6 +1322,11 @@
           <t>Fågelinventering Uvberget Smedjebacken 2023</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113956872</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1399,6 +1434,11 @@
           <t>Fågelinventering Uvberget Smedjebacken 2023</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113956874</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1511,6 +1551,11 @@
           <t>Fågelinventering Uvberget Smedjebacken 2023</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113956875</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1618,6 +1663,11 @@
           <t>Fågelinventering Uvberget Smedjebacken 2023</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113956876</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1725,6 +1775,11 @@
           <t>Fågelinventering Uvberget Smedjebacken 2023</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113956879</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1832,6 +1887,11 @@
           <t>Fågelinventering Uvberget Smedjebacken 2023</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113956883</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1939,6 +1999,11 @@
           <t>Fågelinventering Uvberget Smedjebacken 2023</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113956884</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2046,6 +2111,11 @@
           <t>Fågelinventering Uvberget Smedjebacken 2023</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113956886</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2153,6 +2223,11 @@
           <t>Fågelinventering Uvberget Smedjebacken 2023</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113956887</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2260,6 +2335,11 @@
           <t>Fågelinventering Uvberget Smedjebacken 2023</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113956889</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2367,6 +2447,11 @@
           <t>Fågelinventering Uvberget Smedjebacken 2023</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113956890</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2474,6 +2559,11 @@
           <t>Fågelinventering Uvberget Smedjebacken 2023</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113956892</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2586,6 +2676,11 @@
           <t>Fågelinventering Uvberget Smedjebacken 2023</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113956921</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2688,6 +2783,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130883923</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2793,6 +2893,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134324676</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2898,6 +3003,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134324693</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3003,6 +3113,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134324694</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3108,6 +3223,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134324695</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3213,6 +3333,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134324696</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3318,6 +3443,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134324697</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3423,6 +3553,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134324698</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3528,6 +3663,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134324699</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3633,6 +3773,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134324700</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3738,6 +3883,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134324701</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3843,6 +3993,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134324702</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3948,6 +4103,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134324703</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4053,6 +4213,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134324704</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4150,6 +4315,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134324710</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4250,6 +4420,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134324714</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4355,6 +4530,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134324720</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4460,6 +4640,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134324722</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4565,6 +4750,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134324724</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4670,6 +4860,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134324725</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4775,6 +4970,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134324726</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4880,6 +5080,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134324727</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4985,6 +5190,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134324729</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5090,6 +5300,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134324730</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5195,6 +5410,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134324732</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5300,6 +5520,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134324733</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5405,6 +5630,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134324734</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5510,6 +5740,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134324735</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5615,6 +5850,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134324736</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5720,6 +5960,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134324737</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5825,6 +6070,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134324738</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5930,6 +6180,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134324747</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6035,6 +6290,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134324755</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6140,6 +6400,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134324757</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6245,6 +6510,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134324758</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6350,6 +6620,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134324759</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6455,6 +6730,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134324760</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6560,6 +6840,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134324761</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6665,6 +6950,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134324763</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6770,6 +7060,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134324764</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6875,6 +7170,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134324765</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6980,6 +7280,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134324766</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7085,6 +7390,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134324767</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7190,6 +7500,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134324768</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7299,6 +7614,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130835932</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7405,6 +7725,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134326048</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7506,6 +7831,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130840942</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7607,8 +7937,81 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130840943</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>